--- a/Таблицы для онлайнов/Онлайн я-ИТ-ы №25.xlsx
+++ b/Таблицы для онлайнов/Онлайн я-ИТ-ы №25.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mzaborov\YandexDisk\Работы, тексты, презентации\Я и ТЫ\Поединки\Часы\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\ub-timer\Таблицы для онлайнов\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9DD378-F62D-4189-8093-B32EF6F98EBB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AAED29-FD7C-423F-8872-D5F1BA7930A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{79C00F4D-975F-4909-8A96-898841EE65BD}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>DuelNum</t>
   </si>
@@ -140,6 +140,38 @@
 {
 "Role": "Руководитель консультантов",
 "Goals": "Иметь возможность оперативно решать проблемы пользователей, без лишних препонов и проволочек"
+}
+]</t>
+  </si>
+  <si>
+    <t>Шевчук Александр</t>
+  </si>
+  <si>
+    <t>Кузьмина Екатерина</t>
+  </si>
+  <si>
+    <t>На новом месте</t>
+  </si>
+  <si>
+    <t>&lt;strong&gt;Финансовый директор&lt;/strong&gt; уже год находится в поисках новой работы, но достойного места с зарплатой и кругом обязанностей, соответствующих его уровню профессионализма и опыта, пока не встретилось. Неожиданно &lt;strong&gt;старый знакомый&lt;/strong&gt;, который также работал &lt;strong&gt;финансовым директором&lt;/strong&gt;, но в компании существенно меньшей размером, предлагает ему свое место в связи с переходом на другую работу. При этом зарплата на новом месте в два раза меньше, чем та, на которую рассчитывает &lt;strong&gt;Финансовый директор&lt;/strong&gt;, и сама компания уровнем ниже предыдущей. &lt;strong&gt;Старый знакомый&lt;/strong&gt; говорит, что компания небольшая, но стабильная, работа в финансовом блоке налажена, новых вызовов нет. Нужно только получить новый кредит, но фактически осталось подписать кредитный договор с банком. Подумав, &lt;strong&gt;финансовый директор&lt;/strong&gt; принимает предложение, поскольку других реальных предложений пока нет, и на период поиска хорошего места можно пока поработать здесь. &lt;strong&gt;Финансовый директор&lt;/strong&gt; встречается с &lt;strong&gt;Генеральным директором&lt;/strong&gt; компании, после чего подписывает трудовой договор с условиями, оговоренными ранее со &lt;strong&gt;старым знакомым&lt;/strong&gt;. На встрече эти условия были подтверждены обеими сторонами. Выйдя на работу, &lt;strong&gt;Финансовый директор&lt;/strong&gt; обнаруживает, что работа в финансовом блоке поставлена из рук вон плохо, в его подчинении только &lt;strong&gt;бухгалтерия&lt;/strong&gt; в количестве трех человек, загруженная текущей работой, а банк, о котором шла речь, отказал в предоставлении кредита. При этом зарплата уволившегося &lt;strong&gt;финансового директора&lt;/strong&gt; – &lt;strong&gt;старого знакомого&lt;/strong&gt; – была на треть выше, чем предложенная новому &lt;strong&gt;Финансовому директору&lt;/strong&gt;, кроме того, компания предоставляла ему корпоративный автомобиль. &lt;strong&gt;Генеральный директор&lt;/strong&gt; ставит перед &lt;strong&gt;Финансовым директором&lt;/strong&gt; задачу – получить кредит, и в данном случае это означает «начать все сначала» с несколькими банками. Кроме того, необходимо срочно наладить работу финансового сектора – поставить бюджетирование, учёт себестоимости и другие компоненты. &lt;strong&gt;Финансовый директор&lt;/strong&gt; понимает, какой объем работы неожиданно свалился ему на голову, и его совершенно не прельщает работа в единственном числе – фактически в его распоряжении только &lt;strong&gt;бухгалтерия&lt;/strong&gt;, а ведь на собеседовании говорилось, что в компании есть &lt;strong&gt;экономист&lt;/strong&gt; и вакансия &lt;strong&gt;финансового менеджера&lt;/strong&gt;.</t>
+  </si>
+  <si>
+    <t>[
+{
+"Role": "Финансовый директор",
+"Goals": "увеличить зарплату до уровня не ниже того, что был у него на предыдущем месте работы, поскольку вышло так, что его зарплата теперь меньше, а обязанностей гораздо больше – прежний финансовый директор много чего не доделал. Хочет нанять на работу экономиста и финансового менеджера, поскольку понимает, что объем работ в рамках поставленных задач невозможно выполнить в одиночку."
+},
+{
+"Role": "Генеральный директор",
+"Goals": "сохранить Финансовому директору условия, оговоренные ранее, не увеличивать без необходимости штат, наладить работу финансового сектора, мотивировать Финансового директора на успешное решение поставленных перед ним задач."
+},
+{
+"Role": "Старый знакомый",
+"Goals": "сохранить хорошие отношения со всеми участниками ситуации, не приняв на себя ответственность за ситуацию и не влезая в чужие разборки"
+},
+{
+"Role": "Собственник",
+"Goals": "сохранить Финансового директора для компании, поскольку понимает, что профессионала такого уровня на такую зарплату найти вряд ли удастся. В тоже время, не хочет вмешиваться в зону ответственности Генерального директора, с которым давно работает и которому полностью доверяет."
 }
 ]</t>
   </si>
@@ -598,8 +630,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E5DA1B-597A-4EF5-9C95-CE35359ADEBF}">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="161.25" customHeight="1"/>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultRowHeight="44.25" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="19.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
@@ -611,7 +643,7 @@
     <col min="10" max="10" width="158.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="27" customHeight="1" thickBot="1">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="15.75" thickBot="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -643,7 +675,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" ht="72.75" customHeight="1" thickBot="1">
+    <row r="2" spans="1:10" s="2" customFormat="1" ht="44.25" customHeight="1" thickBot="1">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -675,7 +707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="243" thickBot="1">
+    <row r="3" spans="1:10" ht="44.25" customHeight="1" thickBot="1">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -707,7 +739,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="345" thickBot="1">
+    <row r="4" spans="1:10" ht="44.25" customHeight="1" thickBot="1">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -737,6 +769,38 @@
       </c>
       <c r="J4" s="9" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="44.25" customHeight="1" thickBot="1">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="7">
+        <v>104</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="7">
+        <v>7</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="7">
+        <v>4</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
